--- a/per-stock/LEU/financials.xlsx
+++ b/per-stock/LEU/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3592252416</v>
+        <v>3765176064</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2902652160</v>
+        <v>3075576064</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>66.159424</v>
+        <v>69.3442</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45.994965</v>
+        <v>48.20907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7.9421897</v>
+        <v>8.324510999999999</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-10875000</v>
+        <v>-61400000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>182.6</v>
+        <v>191.39</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,465 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D52</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C52</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B52</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B49:E49)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D50</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C50</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B50</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B47:E47)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D39</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C39</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B39</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B36:E36)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B6:E6)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1864,13 +2332,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1880,7 +2348,6 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1916,11 +2383,6 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
           <t>2024-09-30</t>
         </is>
       </c>
@@ -1931,7 +2393,9 @@
           <t>Tax Effect Of Unusual Items</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
+      <c r="B2" s="3" t="n">
+        <v>3400000</v>
+      </c>
       <c r="C2" s="3" t="n">
         <v>2711267.605634</v>
       </c>
@@ -1944,10 +2408,7 @@
       <c r="F2" s="3" t="n">
         <v>4340909.090909</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>1008000</v>
-      </c>
-      <c r="H2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1955,7 +2416,9 @@
           <t>Tax Rate For Calcs</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
+      <c r="B3" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="C3" s="3" t="n">
         <v>0.164319</v>
       </c>
@@ -1968,10 +2431,7 @@
       <c r="F3" s="3" t="n">
         <v>0.227273</v>
       </c>
-      <c r="G3" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1979,7 +2439,9 @@
           <t>Normalized EBITDA</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
+      <c r="B4" s="3" t="n">
+        <v>1700000</v>
+      </c>
       <c r="C4" s="3" t="n">
         <v>11900000</v>
       </c>
@@ -1992,10 +2454,7 @@
       <c r="F4" s="3" t="n">
         <v>21000000</v>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>47800000</v>
-      </c>
-      <c r="H4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2003,7 +2462,9 @@
           <t>Total Unusual Items</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
+      <c r="B5" s="3" t="n">
+        <v>17000000</v>
+      </c>
       <c r="C5" s="3" t="n">
         <v>16500000</v>
       </c>
@@ -2016,10 +2477,7 @@
       <c r="F5" s="3" t="n">
         <v>19100000</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>4800000</v>
-      </c>
-      <c r="H5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2027,7 +2485,9 @@
           <t>Total Unusual Items Excluding Goodwill</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
+      <c r="B6" s="3" t="n">
+        <v>17000000</v>
+      </c>
       <c r="C6" s="3" t="n">
         <v>16500000</v>
       </c>
@@ -2040,10 +2500,7 @@
       <c r="F6" s="3" t="n">
         <v>19100000</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>4800000</v>
-      </c>
-      <c r="H6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2051,7 +2508,9 @@
           <t>Net Income From Continuing Operation Net Minority Interest</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
+      <c r="B7" s="3" t="n">
+        <v>10000000</v>
+      </c>
       <c r="C7" s="3" t="n">
         <v>17800000</v>
       </c>
@@ -2064,10 +2523,7 @@
       <c r="F7" s="3" t="n">
         <v>27200000</v>
       </c>
-      <c r="G7" s="3" t="n">
-        <v>53700000</v>
-      </c>
-      <c r="H7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2075,7 +2531,9 @@
           <t>Reconciled Depreciation</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
+      <c r="B8" s="3" t="n">
+        <v>2200000</v>
+      </c>
       <c r="C8" s="3" t="n">
         <v>3000000</v>
       </c>
@@ -2088,10 +2546,7 @@
       <c r="F8" s="3" t="n">
         <v>1500000</v>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="H8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2099,7 +2554,9 @@
           <t>Reconciled Cost Of Revenue</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n"/>
+      <c r="B9" s="3" t="n">
+        <v>44800000</v>
+      </c>
       <c r="C9" s="3" t="n">
         <v>110700000</v>
       </c>
@@ -2112,10 +2569,7 @@
       <c r="F9" s="3" t="n">
         <v>39800000</v>
       </c>
-      <c r="G9" s="3" t="n">
-        <v>89500000</v>
-      </c>
-      <c r="H9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2123,7 +2577,9 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n"/>
+      <c r="B10" s="3" t="n">
+        <v>18700000</v>
+      </c>
       <c r="C10" s="3" t="n">
         <v>28400000</v>
       </c>
@@ -2136,10 +2592,7 @@
       <c r="F10" s="3" t="n">
         <v>40100000</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>52600000</v>
-      </c>
-      <c r="H10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2147,7 +2600,9 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="3" t="n">
+        <v>16500000</v>
+      </c>
       <c r="C11" s="3" t="n">
         <v>25400000</v>
       </c>
@@ -2160,10 +2615,7 @@
       <c r="F11" s="3" t="n">
         <v>38600000</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>49700000</v>
-      </c>
-      <c r="H11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2171,7 +2623,9 @@
           <t>Net Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="3" t="n">
+        <v>-4000000</v>
+      </c>
       <c r="C12" s="3" t="n">
         <v>-4100000</v>
       </c>
@@ -2184,10 +2638,7 @@
       <c r="F12" s="3" t="n">
         <v>-3400000</v>
       </c>
-      <c r="G12" s="3" t="n">
-        <v>-1900000</v>
-      </c>
-      <c r="H12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2195,7 +2646,9 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="3" t="n">
+        <v>4000000</v>
+      </c>
       <c r="C13" s="3" t="n">
         <v>4100000</v>
       </c>
@@ -2208,10 +2661,7 @@
       <c r="F13" s="3" t="n">
         <v>3400000</v>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="H13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2219,7 +2669,9 @@
           <t>Normalized Income</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="3" t="n">
+        <v>-3600000</v>
+      </c>
       <c r="C14" s="3" t="n">
         <v>4011267.605634</v>
       </c>
@@ -2232,10 +2684,7 @@
       <c r="F14" s="3" t="n">
         <v>12440909.090909</v>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>49908000</v>
-      </c>
-      <c r="H14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2243,7 +2692,9 @@
           <t>Net Income From Continuing And Discontinued Operation</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="3" t="n">
+        <v>10000000</v>
+      </c>
       <c r="C15" s="3" t="n">
         <v>17800000</v>
       </c>
@@ -2256,10 +2707,7 @@
       <c r="F15" s="3" t="n">
         <v>27200000</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>53700000</v>
-      </c>
-      <c r="H15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2267,7 +2715,9 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
+      <c r="B16" s="3" t="n">
+        <v>75900000</v>
+      </c>
       <c r="C16" s="3" t="n">
         <v>133400000</v>
       </c>
@@ -2280,10 +2730,7 @@
       <c r="F16" s="3" t="n">
         <v>52600000</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>106200000</v>
-      </c>
-      <c r="H16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2291,7 +2738,9 @@
           <t>Total Operating Income As Reported</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
+      <c r="B17" s="3" t="n">
+        <v>800000</v>
+      </c>
       <c r="C17" s="3" t="n">
         <v>12800000</v>
       </c>
@@ -2304,10 +2753,7 @@
       <c r="F17" s="3" t="n">
         <v>20500000</v>
       </c>
-      <c r="G17" s="3" t="n">
-        <v>45100000</v>
-      </c>
-      <c r="H17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2331,7 +2777,6 @@
         <v>17048000</v>
       </c>
       <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2355,7 +2800,6 @@
         <v>16982000</v>
       </c>
       <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2379,7 +2823,6 @@
         <v>1.6</v>
       </c>
       <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2403,7 +2846,6 @@
         <v>1.6</v>
       </c>
       <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2411,7 +2853,9 @@
           <t>Diluted NI Availto Com Stockholders</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n"/>
+      <c r="B22" s="3" t="n">
+        <v>10000000</v>
+      </c>
       <c r="C22" s="3" t="n">
         <v>17800000</v>
       </c>
@@ -2424,10 +2868,7 @@
       <c r="F22" s="3" t="n">
         <v>27200000</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>53700000</v>
-      </c>
-      <c r="H22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2435,7 +2876,9 @@
           <t>Net Income Common Stockholders</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n"/>
+      <c r="B23" s="3" t="n">
+        <v>10000000</v>
+      </c>
       <c r="C23" s="3" t="n">
         <v>17800000</v>
       </c>
@@ -2448,10 +2891,7 @@
       <c r="F23" s="3" t="n">
         <v>27200000</v>
       </c>
-      <c r="G23" s="3" t="n">
-        <v>53700000</v>
-      </c>
-      <c r="H23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2459,7 +2899,9 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
+      <c r="B24" s="3" t="n">
+        <v>10000000</v>
+      </c>
       <c r="C24" s="3" t="n">
         <v>17800000</v>
       </c>
@@ -2472,10 +2914,7 @@
       <c r="F24" s="3" t="n">
         <v>27200000</v>
       </c>
-      <c r="G24" s="3" t="n">
-        <v>53700000</v>
-      </c>
-      <c r="H24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2483,7 +2922,9 @@
           <t>Net Income Including Noncontrolling Interests</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n"/>
+      <c r="B25" s="3" t="n">
+        <v>10000000</v>
+      </c>
       <c r="C25" s="3" t="n">
         <v>17800000</v>
       </c>
@@ -2496,10 +2937,7 @@
       <c r="F25" s="3" t="n">
         <v>27200000</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>53700000</v>
-      </c>
-      <c r="H25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2507,7 +2945,9 @@
           <t>Net Income Continuous Operations</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n"/>
+      <c r="B26" s="3" t="n">
+        <v>10000000</v>
+      </c>
       <c r="C26" s="3" t="n">
         <v>17800000</v>
       </c>
@@ -2520,10 +2960,7 @@
       <c r="F26" s="3" t="n">
         <v>27200000</v>
       </c>
-      <c r="G26" s="3" t="n">
-        <v>53700000</v>
-      </c>
-      <c r="H26" s="3" t="n"/>
+      <c r="G26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2531,7 +2968,9 @@
           <t>Tax Provision</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n"/>
+      <c r="B27" s="3" t="n">
+        <v>2500000</v>
+      </c>
       <c r="C27" s="3" t="n">
         <v>3500000</v>
       </c>
@@ -2544,10 +2983,7 @@
       <c r="F27" s="3" t="n">
         <v>8000000</v>
       </c>
-      <c r="G27" s="3" t="n">
-        <v>-5900000</v>
-      </c>
-      <c r="H27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2555,7 +2991,9 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n"/>
+      <c r="B28" s="3" t="n">
+        <v>12500000</v>
+      </c>
       <c r="C28" s="3" t="n">
         <v>21300000</v>
       </c>
@@ -2568,10 +3006,7 @@
       <c r="F28" s="3" t="n">
         <v>35200000</v>
       </c>
-      <c r="G28" s="3" t="n">
-        <v>47800000</v>
-      </c>
-      <c r="H28" s="3" t="n"/>
+      <c r="G28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2579,7 +3014,9 @@
           <t>Other Income Expense</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n"/>
+      <c r="B29" s="3" t="n">
+        <v>15700000</v>
+      </c>
       <c r="C29" s="3" t="n">
         <v>12600000</v>
       </c>
@@ -2592,10 +3029,7 @@
       <c r="F29" s="3" t="n">
         <v>18100000</v>
       </c>
-      <c r="G29" s="3" t="n">
-        <v>4300000</v>
-      </c>
-      <c r="H29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2603,7 +3037,9 @@
           <t>Other Non Operating Income Expenses</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n"/>
+      <c r="B30" s="3" t="n">
+        <v>-1300000</v>
+      </c>
       <c r="C30" s="3" t="n">
         <v>-3900000</v>
       </c>
@@ -2616,10 +3052,7 @@
       <c r="F30" s="3" t="n">
         <v>-1000000</v>
       </c>
-      <c r="G30" s="3" t="n">
-        <v>-500000</v>
-      </c>
-      <c r="H30" s="3" t="n"/>
+      <c r="G30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2627,7 +3060,9 @@
           <t>Special Income Charges</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n"/>
+      <c r="B31" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="C31" s="3" t="n">
         <v>0</v>
       </c>
@@ -2641,7 +3076,6 @@
         <v>11800000</v>
       </c>
       <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2659,7 +3093,6 @@
         <v>-11800000</v>
       </c>
       <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2667,7 +3100,9 @@
           <t>Gain On Sale Of Security</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n"/>
+      <c r="B33" s="3" t="n">
+        <v>17000000</v>
+      </c>
       <c r="C33" s="3" t="n">
         <v>16500000</v>
       </c>
@@ -2680,10 +3115,7 @@
       <c r="F33" s="3" t="n">
         <v>7300000</v>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>5100000</v>
-      </c>
-      <c r="H33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2691,7 +3123,9 @@
           <t>Net Non Operating Interest Income Expense</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n"/>
+      <c r="B34" s="3" t="n">
+        <v>-4000000</v>
+      </c>
       <c r="C34" s="3" t="n">
         <v>-4100000</v>
       </c>
@@ -2704,10 +3138,7 @@
       <c r="F34" s="3" t="n">
         <v>-3400000</v>
       </c>
-      <c r="G34" s="3" t="n">
-        <v>-1900000</v>
-      </c>
-      <c r="H34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2715,7 +3146,9 @@
           <t>Interest Expense Non Operating</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n"/>
+      <c r="B35" s="3" t="n">
+        <v>4000000</v>
+      </c>
       <c r="C35" s="3" t="n">
         <v>4100000</v>
       </c>
@@ -2728,10 +3161,7 @@
       <c r="F35" s="3" t="n">
         <v>3400000</v>
       </c>
-      <c r="G35" s="3" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="H35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2739,7 +3169,9 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n"/>
+      <c r="B36" s="3" t="n">
+        <v>800000</v>
+      </c>
       <c r="C36" s="3" t="n">
         <v>12800000</v>
       </c>
@@ -2752,10 +3184,7 @@
       <c r="F36" s="3" t="n">
         <v>20500000</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>45400000</v>
-      </c>
-      <c r="H36" s="3" t="n"/>
+      <c r="G36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2763,7 +3192,9 @@
           <t>Operating Expense</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n"/>
+      <c r="B37" s="3" t="n">
+        <v>30700000</v>
+      </c>
       <c r="C37" s="3" t="n">
         <v>22200000</v>
       </c>
@@ -2776,10 +3207,7 @@
       <c r="F37" s="3" t="n">
         <v>12400000</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>16400000</v>
-      </c>
-      <c r="H37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2787,7 +3215,9 @@
           <t>Other Operating Expenses</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n"/>
+      <c r="B38" s="3" t="n">
+        <v>18900000</v>
+      </c>
       <c r="C38" s="3" t="n">
         <v>8900000</v>
       </c>
@@ -2800,10 +3230,7 @@
       <c r="F38" s="3" t="n">
         <v>3000000</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>3300000</v>
-      </c>
-      <c r="H38" s="3" t="n"/>
+      <c r="G38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2811,7 +3238,9 @@
           <t>Depreciation Amortization Depletion Income Statement</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n"/>
+      <c r="B39" s="3" t="n">
+        <v>1800000</v>
+      </c>
       <c r="C39" s="3" t="n">
         <v>2500000</v>
       </c>
@@ -2824,10 +3253,7 @@
       <c r="F39" s="3" t="n">
         <v>1100000</v>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="H39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2835,7 +3261,9 @@
           <t>Depreciation And Amortization In Income Statement</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n"/>
+      <c r="B40" s="3" t="n">
+        <v>1800000</v>
+      </c>
       <c r="C40" s="3" t="n">
         <v>2500000</v>
       </c>
@@ -2848,10 +3276,7 @@
       <c r="F40" s="3" t="n">
         <v>1100000</v>
       </c>
-      <c r="G40" s="3" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="H40" s="3" t="n"/>
+      <c r="G40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2859,7 +3284,9 @@
           <t>Amortization</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n"/>
+      <c r="B41" s="3" t="n">
+        <v>1800000</v>
+      </c>
       <c r="C41" s="3" t="n">
         <v>2500000</v>
       </c>
@@ -2872,10 +3299,7 @@
       <c r="F41" s="3" t="n">
         <v>1100000</v>
       </c>
-      <c r="G41" s="3" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="H41" s="3" t="n"/>
+      <c r="G41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2883,7 +3307,9 @@
           <t>Amortization Of Intangibles Income Statement</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n"/>
+      <c r="B42" s="3" t="n">
+        <v>1800000</v>
+      </c>
       <c r="C42" s="3" t="n">
         <v>2500000</v>
       </c>
@@ -2896,10 +3322,7 @@
       <c r="F42" s="3" t="n">
         <v>1100000</v>
       </c>
-      <c r="G42" s="3" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="H42" s="3" t="n"/>
+      <c r="G42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2907,7 +3330,9 @@
           <t>Selling General And Administration</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n"/>
+      <c r="B43" s="3" t="n">
+        <v>10000000</v>
+      </c>
       <c r="C43" s="3" t="n">
         <v>10800000</v>
       </c>
@@ -2920,10 +3345,7 @@
       <c r="F43" s="3" t="n">
         <v>8300000</v>
       </c>
-      <c r="G43" s="3" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="H43" s="3" t="n"/>
+      <c r="G43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2942,8 +3364,7 @@
         <v>13400000</v>
       </c>
       <c r="F44" s="3" t="n"/>
-      <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="n">
+      <c r="G44" s="3" t="n">
         <v>10000000</v>
       </c>
     </row>
@@ -2964,8 +3385,7 @@
         <v>9200000</v>
       </c>
       <c r="F45" s="3" t="n"/>
-      <c r="G45" s="3" t="n"/>
-      <c r="H45" s="3" t="n">
+      <c r="G45" s="3" t="n">
         <v>9600000</v>
       </c>
     </row>
@@ -2987,7 +3407,6 @@
       </c>
       <c r="F46" s="3" t="n"/>
       <c r="G46" s="3" t="n"/>
-      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2995,7 +3414,9 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n"/>
+      <c r="B47" s="3" t="n">
+        <v>31500000</v>
+      </c>
       <c r="C47" s="3" t="n">
         <v>35000000</v>
       </c>
@@ -3008,10 +3429,7 @@
       <c r="F47" s="3" t="n">
         <v>32900000</v>
       </c>
-      <c r="G47" s="3" t="n">
-        <v>61800000</v>
-      </c>
-      <c r="H47" s="3" t="n"/>
+      <c r="G47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3019,7 +3437,9 @@
           <t>Cost Of Revenue</t>
         </is>
       </c>
-      <c r="B48" s="3" t="n"/>
+      <c r="B48" s="3" t="n">
+        <v>45200000</v>
+      </c>
       <c r="C48" s="3" t="n">
         <v>111200000</v>
       </c>
@@ -3032,10 +3452,7 @@
       <c r="F48" s="3" t="n">
         <v>40200000</v>
       </c>
-      <c r="G48" s="3" t="n">
-        <v>89800000</v>
-      </c>
-      <c r="H48" s="3" t="n"/>
+      <c r="G48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3043,7 +3460,9 @@
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="B49" s="3" t="n"/>
+      <c r="B49" s="3" t="n">
+        <v>76700000</v>
+      </c>
       <c r="C49" s="3" t="n">
         <v>146200000</v>
       </c>
@@ -3056,10 +3475,7 @@
       <c r="F49" s="3" t="n">
         <v>73100000</v>
       </c>
-      <c r="G49" s="3" t="n">
-        <v>151600000</v>
-      </c>
-      <c r="H49" s="3" t="n"/>
+      <c r="G49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3067,7 +3483,9 @@
           <t>Operating Revenue</t>
         </is>
       </c>
-      <c r="B50" s="3" t="n"/>
+      <c r="B50" s="3" t="n">
+        <v>76700000</v>
+      </c>
       <c r="C50" s="3" t="n">
         <v>146200000</v>
       </c>
@@ -3080,17 +3498,14 @@
       <c r="F50" s="3" t="n">
         <v>73100000</v>
       </c>
-      <c r="G50" s="3" t="n">
-        <v>151600000</v>
-      </c>
-      <c r="H50" s="3" t="n"/>
+      <c r="G50" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4552,7 +4967,1679 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H71"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>19671587</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>19664565</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>18212032</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>18207842</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>17036021</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>19671587</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>19664565</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>18212032</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>18207842</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>17036021</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1178600000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1215200000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1247800000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>429800000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>457600000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>755800000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>743900000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>339400000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>334300000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>185400000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1953800000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1978800000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1610900000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>788900000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>671500000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1894100000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1940800000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1538400000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>768400000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>644900000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>755800000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>743900000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>339400000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>334300000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>185400000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>775200000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>765100000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>363100000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>359100000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>213900000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>1951300000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1939900000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1570600000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>749100000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>631700000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>775200000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>765100000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>363100000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>359100000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>213900000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>775200000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>765100000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>363100000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>359100000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>213900000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>-700000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>-700000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>-700000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-600000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>-600000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-700000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-700000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-700000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-600000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-600000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-16300000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-20200000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-49100000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>762400000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>762300000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>378300000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>378100000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>261900000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>1658000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>1680800000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1881800000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>955700000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>1080000000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1256700000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1258000000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1255600000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>473500000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>502200000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>7300000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-25700000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>8700000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Employee Benefits</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>73300000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>75200000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>73800000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>74800000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>76400000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Non Current Pension And Other Postretirement Benefit Plans</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>73300000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>75200000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>73800000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>74800000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>76400000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1176100000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1174800000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1207500000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>390000000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>417800000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>1176100000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1174800000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1207500000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>390000000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>417800000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>401300000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>422800000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>626200000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>482200000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>577800000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>170800000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>192700000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>238900000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>127400000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>203900000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>112800000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>131100000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>154800000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>154800000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>216500000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>112800000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>131100000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>154800000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>154800000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>216500000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>40400000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>40300000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>39800000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>39800000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>38900000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>40300000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>39800000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>39800000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>38900000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>40300000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>39800000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>39800000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="3" t="n">
+        <v>25800000</v>
+      </c>
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="3" t="n"/>
+      <c r="F38" s="3" t="n"/>
+      <c r="G38" s="3" t="n">
+        <v>29400000</v>
+      </c>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>115200000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>32800000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>192200000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>160200000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>117600000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n">
+        <v>4300000</v>
+      </c>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="3" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Interest Payable</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>115200000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>28500000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>192200000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>160200000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>117600000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Other Payable</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>65700000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>18500000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>155900000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>127100000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>85100000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>49500000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>36300000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>33100000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>32500000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>2433200000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>2445900000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>2244900000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>1314800000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>1293900000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>137800000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>82300000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>80300000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>64200000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>71200000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>6600000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>7700000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Non Current Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>32800000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>21900000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>25800000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>13900000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>21800000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>21900000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>25800000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>13900000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>21800000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>19400000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>21200000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>23700000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>24800000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>28500000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>19400000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>21200000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>23700000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>24800000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>28500000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>59500000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>29500000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>20500000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>14900000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>11200000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>-7100000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>-6700000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>-6300000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>-5900000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>-5500000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>66600000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>36200000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>26800000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>20800000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>16700000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n">
+        <v>21600000</v>
+      </c>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n"/>
+      <c r="D57" s="3" t="n"/>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n"/>
+      <c r="C58" s="3" t="n">
+        <v>6600000</v>
+      </c>
+      <c r="D58" s="3" t="n"/>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="3" t="n">
+        <v>6800000</v>
+      </c>
+      <c r="D59" s="3" t="n"/>
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>2295400000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>2363600000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>2164600000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>1250600000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>1222700000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>12400000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>11900000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>8100000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>18100000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>37500000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>40900000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>47700000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>47700000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>63900000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>336000000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>322900000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>416300000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>320500000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>429600000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Other Inventories</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>30100000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>21100000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>22100000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>17100000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>17800000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>305900000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>301800000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>394200000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>303400000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>411800000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>41800000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>30700000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>60700000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>31300000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>38700000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>19100000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>10800000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>16600000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>9900000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>22700000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>44100000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>21400000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>29700000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>1868200000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>1957200000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>1631800000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>833000000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>653000000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>1868200000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>1957200000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>1631800000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>833000000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>653000000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5650,13 +7737,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5666,6 +7753,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5676,30 +7764,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -5712,21 +7805,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-58300000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-58000000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>5700000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>49200000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>34400000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>57200000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5744,10 +7838,13 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>-74300000</v>
       </c>
-      <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5755,14 +7852,15 @@
           <t>Issuance Of Debt</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5771,21 +7869,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>384000000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-200000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>114700000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>25200000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>31300000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5794,21 +7893,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-23200000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-9600000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-4400000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-3600000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-2100000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>-700000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5816,16 +7916,17 @@
           <t>Interest Paid Supplemental Data</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n">
         <v>4500000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n"/>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5833,18 +7934,19 @@
           <t>Income Tax Paid Supplemental Data</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n">
         <v>300000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>100000</v>
       </c>
-      <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n">
         <v>100000</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="H8" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5855,21 +7957,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>1901200000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>1960100000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>1634600000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>847000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>685700000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>704000000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5878,21 +7981,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>1960100000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>1634600000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>847000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>685700000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>704000000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>226900000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5901,21 +8005,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-300000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>100000</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>-100000</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>-100000</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>200000</v>
+        <v>-100000</v>
       </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5924,21 +8029,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-58600000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>325500000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>787500000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>161400000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-18200000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>476900000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5947,21 +8053,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>-300000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>383500000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>781800000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>112200000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>-52600000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>419700000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5970,21 +8077,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-300000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>383500000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>781800000</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>111900000</v>
-      </c>
       <c r="E14" s="3" t="n">
-        <v>-52300000</v>
+        <v>112200000</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>419700000</v>
+        <v>-52600000</v>
       </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5995,11 +8103,12 @@
       <c r="B15" s="3" t="n"/>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n">
         <v>-300000</v>
       </c>
-      <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6017,12 +8126,13 @@
         <v>0</v>
       </c>
       <c r="E16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="n">
         <v>-3500000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6031,21 +8141,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>-300000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>-500000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>-400000</v>
       </c>
-      <c r="D17" s="3" t="n">
-        <v>-2800000</v>
-      </c>
       <c r="E17" s="3" t="n">
-        <v>300000</v>
+        <v>-2500000</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-300000</v>
+        <v>0</v>
       </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6069,6 +8180,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6077,21 +8189,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>384000000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>-200000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>114700000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>25200000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>31300000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6100,21 +8213,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>384000000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>-200000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>114700000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>25200000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>31300000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6126,16 +8240,19 @@
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
         <v>782400000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-74300000</v>
       </c>
-      <c r="F21" s="3" t="n"/>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6147,16 +8264,19 @@
         <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
         <v>782400000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-74300000</v>
       </c>
-      <c r="F22" s="3" t="n"/>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6174,10 +8294,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="n">
         <v>-74300000</v>
       </c>
-      <c r="F23" s="3" t="n"/>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6185,14 +8308,15 @@
           <t>Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n"/>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6201,21 +8325,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-23200000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-9600000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-4400000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-3600000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-2100000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>-700000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6224,21 +8349,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-23200000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-9600000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-4400000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-3600000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-2100000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>-700000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6247,21 +8373,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-23200000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-9600000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-4400000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-3600000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-2100000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>-700000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6270,21 +8397,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>-35100000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-48400000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>10100000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>52800000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>36500000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>57900000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6293,21 +8421,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-35100000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-48400000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>10100000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>52800000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>36500000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>57900000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6316,21 +8445,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-51200000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-77300000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>14700000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>5600000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>8900000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>9100000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6339,21 +8469,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-16400000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-17700000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-1100000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-14400000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>-2200000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>2600000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6362,21 +8493,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-600000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>-1100000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>500000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>800000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>-600000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6385,21 +8517,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>47600000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-132500000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>30400000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>42100000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>49400000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>36900000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6408,21 +8541,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>47600000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>-132500000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>30400000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>42100000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>49400000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>36900000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6431,21 +8565,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>4900000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>1600000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>100000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>-6200000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>7400000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6454,21 +8589,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>-70700000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>40900000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>15900000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>-29900000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>-80400000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>31000000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6477,21 +8613,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>-11100000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>30000000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>-29400000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>7300000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>41300000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>-60800000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6500,21 +8637,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>-11100000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>30000000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>-29400000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>7300000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>41300000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>-60800000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6523,21 +8661,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>900000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>1300000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>2200000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>2700000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>-1500000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6546,21 +8685,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>500000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>600000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>4200000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>500000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>400000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6569,21 +8709,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>3800000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>-11900000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>8000000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>7500000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>-6200000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6592,21 +8733,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>3800000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>-11900000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>8000000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>7500000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>-6200000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6615,21 +8757,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>3000000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>1500000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>3900000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>1500000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>2900000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6638,21 +8781,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>3000000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>1500000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>3900000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>1500000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>2900000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6660,22 +8804,23 @@
           <t>Operating Gains Losses</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n">
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3" t="n">
         <v>2900000</v>
-      </c>
-      <c r="C45" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3" t="n">
         <v>-11800000</v>
       </c>
-      <c r="F45" s="3" t="n">
+      <c r="G45" s="3" t="n">
         <v>-500000</v>
       </c>
-      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6683,18 +8828,19 @@
           <t>Pension And Employee Benefit Expense</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n">
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n">
         <v>2900000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D46" s="3" t="n"/>
       <c r="E46" s="3" t="n"/>
-      <c r="F46" s="3" t="n">
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n">
         <v>-500000</v>
       </c>
-      <c r="G46" s="3" t="n">
+      <c r="H46" s="3" t="n">
         <v>-200000</v>
       </c>
     </row>
@@ -6705,28 +8851,29 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>17800000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>3900000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>28900000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>27200000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>53700000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6754,12 +8901,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FY Summary</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>no gaps detected</t>
+          <t>'Net Debt' not found in statements — left blank</t>
         </is>
       </c>
     </row>
